--- a/samples/M_科目余额表.xlsx
+++ b/samples/M_科目余额表.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -508,19 +508,19 @@
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>280000</v>
+        <v>650000</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>3200000</v>
+        <v>8500000</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>3240000</v>
+        <v>9200000</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>320000</v>
+        <v>1350000</v>
       </c>
     </row>
     <row r="3">
@@ -538,19 +538,19 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>150000</v>
+        <v>350000</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1800000</v>
+        <v>5200000</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1820000</v>
+        <v>5800000</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>170000</v>
+        <v>950000</v>
       </c>
     </row>
     <row r="4">
@@ -561,26 +561,26 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>应交税费-企业所得税</t>
+          <t>应交税费-所得税</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1100000</v>
+        <v>2500000</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1120000</v>
+        <v>2600000</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>120000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="5">
@@ -591,26 +591,116 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>应交税费-附加税</t>
+          <t>应交税费-城建税</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>364000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>406000</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>92000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>222104</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>应交税费-教育费附加</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>30000</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>300000</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>30000</v>
+      <c r="E6" s="3" t="n">
+        <v>218400</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>243600</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>55200</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>222105</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>应交税费-地方教育附加</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>145600</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>162400</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>36800</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>222106</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>应交税费-印花税</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
